--- a/product_selector_out/STM32U5F9-5G9.xlsx
+++ b/product_selector_out/STM32U5F9-5G9.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,17 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -103,8 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1314,7 +1302,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1629,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1956,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2283,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2610,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2937,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3264,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3591,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4213,9 +4201,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4228,17 +4216,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4253,7 +4241,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4263,12 +4251,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4278,14 +4266,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4313,12 +4301,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4348,12 +4336,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4363,7 +4351,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4373,7 +4361,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4418,12 +4406,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4433,19 +4421,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -4463,42 +4451,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4513,9 +4501,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4540,9 +4528,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4555,17 +4543,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4580,7 +4568,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4590,12 +4578,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4605,14 +4593,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4640,12 +4628,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4675,12 +4663,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4690,7 +4678,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4700,7 +4688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4745,12 +4733,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4760,19 +4748,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -4790,42 +4778,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4840,9 +4828,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4867,9 +4855,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4882,17 +4870,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4907,7 +4895,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4917,12 +4905,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4932,14 +4920,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4967,12 +4955,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5002,12 +4990,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5017,7 +5005,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5027,7 +5015,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="8" t="inlineStr">
+      <c r="AK14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5072,12 +5060,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5087,19 +5075,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -5117,42 +5105,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5167,9 +5155,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5194,9 +5182,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5209,17 +5197,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5234,7 +5222,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5244,12 +5232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5259,14 +5247,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5294,12 +5282,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5329,12 +5317,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5344,7 +5332,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5354,7 +5342,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5399,12 +5387,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5414,19 +5402,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -5444,42 +5432,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5494,9 +5482,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5521,9 +5509,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5536,17 +5524,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5561,7 +5549,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5571,12 +5559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5586,14 +5574,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5621,12 +5609,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5656,12 +5644,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5671,7 +5659,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5681,7 +5669,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5726,12 +5714,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5741,19 +5729,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -5771,42 +5759,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5821,9 +5809,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5848,9 +5836,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5863,17 +5851,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5888,7 +5876,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5898,12 +5886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5913,14 +5901,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -5948,12 +5936,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5988,7 +5976,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5998,7 +5986,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6008,7 +5996,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6053,12 +6041,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6068,19 +6056,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -6098,42 +6086,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6148,9 +6136,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6175,9 +6163,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6190,17 +6178,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6215,7 +6203,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6225,12 +6213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6240,14 +6228,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6275,12 +6263,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6315,7 +6303,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6325,7 +6313,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6335,7 +6323,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="8" t="inlineStr">
+      <c r="AK18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6380,12 +6368,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="8" t="inlineStr">
+      <c r="AT18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6395,19 +6383,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -6425,42 +6413,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6475,9 +6463,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6502,9 +6490,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6517,17 +6505,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6542,7 +6530,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6552,12 +6540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6567,14 +6555,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6602,12 +6590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6642,7 +6630,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6652,7 +6640,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6662,7 +6650,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="8" t="inlineStr">
+      <c r="AK19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6707,12 +6695,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="8" t="inlineStr">
+      <c r="AT19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6722,19 +6710,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -6752,42 +6740,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6802,9 +6790,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6854,710 +6842,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STM32U5F9VJ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32U5F9VJ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32U5F9VJ</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32U5F9VJ</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32U5F9NJ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32U5F9NJ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32U5F9NJ</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32U5F9NJ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32U5F9BJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32U5F9BJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32U5F9BJ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32U5F9BJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32U5G9BJ</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32U5G9BJ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32U5G9BJ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32U5G9BJ</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32U5F9ZJ</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32U5F9ZJ</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32U5F9ZJ</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32U5F9ZJ</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32U5G9ZJ</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32U5G9ZJ</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32U5G9ZJ</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32U5G9ZJ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32U5G9VJ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32U5G9VJ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32U5G9VJ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32U5G9VJ</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32U5G9NJ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32U5G9NJ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32U5G9NJ</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32U5G9NJ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 73. Typical dynamic current consumption of peripherals</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32U5F9-5G9.xlsx
+++ b/product_selector_out/STM32U5F9-5G9.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,7 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -93,6 +103,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1302,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
@@ -4201,9 +4213,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4216,17 +4228,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4241,7 +4253,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4251,12 +4263,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4266,14 +4278,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4301,12 +4313,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4336,12 +4348,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4351,7 +4363,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4361,7 +4373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4406,12 +4418,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4421,19 +4433,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -4451,42 +4463,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4501,9 +4513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4528,9 +4540,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4543,17 +4555,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4568,7 +4580,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4578,12 +4590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4593,14 +4605,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4628,12 +4640,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4663,12 +4675,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4678,7 +4690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4688,7 +4700,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4733,12 +4745,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4748,19 +4760,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -4778,42 +4790,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4828,9 +4840,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4855,9 +4867,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4870,17 +4882,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4895,7 +4907,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4905,12 +4917,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4920,14 +4932,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4955,12 +4967,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4990,12 +5002,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5005,7 +5017,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5015,7 +5027,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="7" t="inlineStr">
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5060,12 +5072,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5075,19 +5087,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -5105,42 +5117,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5155,9 +5167,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5182,9 +5194,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5197,17 +5209,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5222,7 +5234,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5232,12 +5244,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5247,14 +5259,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5282,12 +5294,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5317,12 +5329,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5332,7 +5344,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5342,7 +5354,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5387,12 +5399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5402,19 +5414,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -5432,42 +5444,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5482,9 +5494,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5509,9 +5521,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5524,17 +5536,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5549,7 +5561,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5559,12 +5571,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5574,14 +5586,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5609,12 +5621,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5644,12 +5656,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5659,7 +5671,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5669,7 +5681,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5714,12 +5726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5729,19 +5741,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -5759,42 +5771,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5809,9 +5821,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5836,9 +5848,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5851,17 +5863,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5876,7 +5888,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5886,12 +5898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5901,14 +5913,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -5936,12 +5948,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5976,7 +5988,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="AG17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5986,7 +5998,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5996,7 +6008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6041,12 +6053,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6056,19 +6068,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -6086,42 +6098,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6136,9 +6148,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6163,9 +6175,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6178,17 +6190,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6203,7 +6215,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6213,12 +6225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6228,14 +6240,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6263,12 +6275,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6303,7 +6315,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="7" t="inlineStr">
+      <c r="AG18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6313,7 +6325,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6323,7 +6335,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
+      <c r="AK18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6368,12 +6380,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="7" t="inlineStr">
+      <c r="AT18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6383,19 +6395,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -6413,42 +6425,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6463,9 +6475,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6490,9 +6502,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6505,17 +6517,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6530,7 +6542,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6540,12 +6552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6555,14 +6567,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6590,12 +6602,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6630,7 +6642,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6640,7 +6652,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6650,7 +6662,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="7" t="inlineStr">
+      <c r="AK19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6695,12 +6707,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="7" t="inlineStr">
+      <c r="AT19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6710,19 +6722,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -6740,42 +6752,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6790,9 +6802,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6842,7 +6854,886 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32U5F9VJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32U5F9VJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32U5F9VJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32U5F9VJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32U5F9VJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32U5F9NJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32U5F9NJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32U5F9NJ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32U5F9NJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32U5F9NJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32U5F9BJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32U5F9BJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32U5F9BJ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32U5F9BJ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32U5F9BJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32U5G9BJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32U5G9BJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32U5G9BJ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32U5G9BJ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32U5G9BJ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32U5F9ZJ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32U5F9ZJ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 19. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32U5F9ZJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32U5F9ZJ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32U5F9ZJ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32U5G9ZJ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32U5G9ZJ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32U5G9ZJ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32U5G9ZJ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32U5G9ZJ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32U5G9VJ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32U5G9VJ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32U5G9VJ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32U5G9VJ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32U5G9VJ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32U5G9NJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32U5G9NJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32U5G9NJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32U5G9NJ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32U5G9NJ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 73. Typical dynamic current consumption of peripherals</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32U5F9-5G9.xlsx
+++ b/product_selector_out/STM32U5F9-5G9.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
@@ -3603,12 +3645,17 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3629,16 +3676,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3651,6 +3696,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3670,7 +3716,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3695,7 +3743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3763,6 +3811,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4096,6 +4145,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4191,6 +4245,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4513,7 +4568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4840,7 +4900,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5167,7 +5232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5494,7 +5564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5821,7 +5896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6148,7 +6228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6475,7 +6560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6802,7 +6892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6810,8 +6905,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
